--- a/첨삭/[숨죽인 꿈] 버전/호흡 시스템.xlsx
+++ b/첨삭/[숨죽인 꿈] 버전/호흡 시스템.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="16710" windowHeight="8640"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="21345" windowHeight="8640"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="01_시스템데이터" sheetId="1" r:id="rId4"/>
@@ -507,7 +507,154 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="286">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="287">
+  <x:si>
+    <x:t>별도 호흡 입력이 없는 기본 상태 / 
+참기·날숨 중 호흡량 0 도달 시 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>입력 유지 중 증가 / 다른 행동 입력 시 전환 /
+키 해제 시 자동 날숨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>※ 과흡입·강제 호흡 등 실패 이벤트 발생 시간은 구간 통과 계산에서 제외</x:t>
+  </x:si>
+  <x:si>
+    <x:t>날숨 중 호흡량 0 도달 전부터 유지한 입력은 새 입력으로 판정하지 않음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외형 판별을 통과해도 유효 청각 거리 안의 호흡 소리는 인간 판별 단서가 됨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참기 유지 · 날숨 여부를 조절하며 다음 공기 지점까지 호흡량 관리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직접 조작 불가 / 시스템상 평상 호흡 / 호흡량 -50/s → 0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유해 연기 발생 → 오염도 신규 누적
+/ 기존 자극도는 그대로 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>꽃가루</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행동명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>없음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>값</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>들숨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>독가스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>연기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>처리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특징</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과흡입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안전</x:t>
+  </x:si>
+  <x:si>
+    <x:t>분류</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오염도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구분</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상태</x:t>
+  </x:si>
+  <x:si>
+    <x:t>환경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달리기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수영</x:t>
+  </x:si>
+  <x:si>
+    <x:t>걷기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>미감지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>날숨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>비고</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>참기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시야각</x:t>
+  </x:si>
+  <x:si>
+    <x:t>결과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>콘텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>먼지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90˚</x:t>
+  </x:si>
   <x:si>
     <x:t xml:space="preserve">사용 방법 ｜ 왼쪽 '입력 항목'의 값을 입력·선택하면, 오른쪽 '산출 항목'의 결과가 자동 계산됩니다. </x:t>
   </x:si>
@@ -516,27 +663,21 @@
 키 해제 시 자동 날숨 / 0 도달 시 평상 호흡</x:t>
   </x:si>
   <x:si>
-    <x:t>참기·이동 소리·청각 감지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극 이상 + 오염 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수면 / 공기 주머니 표시</x:t>
-  </x:si>
-  <x:si>
     <x:t>자극도·오염도 신규 누적·회복 없음 /
 참기·날숨은 기존 호흡 행동 규칙 적용 / 들숨 시 호흡량 -100/s</x:t>
   </x:si>
   <x:si>
+    <x:t>호흡량 100 / 조작 재개</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해당 구역 유해 공기 → 안전 공기로 영구 전환 
+/ 이후 안전 공기 회복 규칙 적용</x:t>
+  </x:si>
+  <x:si>
     <x:t>시작 후 호흡량 0까지 자동 진행 / 중도 전환 불가 /
 0 도달 시 평상 호흡 전환</x:t>
   </x:si>
   <x:si>
-    <x:t>해당 구역 유해 공기 → 안전 공기로 영구 전환 
-/ 이후 안전 공기 회복 규칙 적용</x:t>
-  </x:si>
-  <x:si>
     <x:t>오염도 누적 /
 안전 공기를 거치지 않고 자극 환경으로 이동 시 현재 오염도 유지</x:t>
   </x:si>
@@ -556,826 +697,688 @@
 안전 공기를 거치지 않고 자극 환경으로 이동 시 현재 오염도 유지</x:t>
   </x:si>
   <x:si>
-    <x:t>※ 과흡입·강제 호흡 등 실패 이벤트 발생 시간은 구간 통과 계산에서 제외</x:t>
-  </x:si>
-  <x:si>
-    <x:t>외형 판별을 통과해도 유효 청각 거리 안의 호흡 소리는 인간 판별 단서가 됨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>입력 유지 중 증가 / 다른 행동 입력 시 전환 /
-키 해제 시 자동 날숨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>날숨 중 호흡량 0 도달 전부터 유지한 입력은 새 입력으로 판정하지 않음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>별도 호흡 입력이 없는 기본 상태 / 
-참기·날숨 중 호흡량 0 도달 시 전환</x:t>
+    <x:t>안전하게 돌아가기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참기 유지 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>들숨·회복 후 재진입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>청각 중심 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 구간 준비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>계산·검증 시트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주요 자원 판단</x:t>
+  </x:si>
+  <x:si>
+    <x:t>신규 자극도 누적 차단</x:t>
+  </x:si>
+  <x:si>
+    <x:t>벽·가구 + 일반 인형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. 호흡 실패 이벤트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BREATH_NORMAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BREATH_EXHALE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시간 경과에 따라 다음 단계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무소음 이동 가능 거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>욕조·침수 공간·공기 주머니</x:t>
+  </x:si>
+  <x:si>
+    <x:t>긴 이동 + 중간 안전 지점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안전 공기에서 오염도 0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거리 짧음 / 위험 높음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수면 / 공기 주머니 표시</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통과 시간 / 현재 자극도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>외형 판별 + 호흡 소리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참기 시 이동 소리 0m</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡량 확보 / 상태 회복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6. 인형 감지 데이터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참기·이동 소리·청각 감지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극 이상 + 오염 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. 공기 환경 및 수중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시야 방향 / 순찰 동선</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참기 + 웅크려 이동 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현재 행동 기준 통과 판정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7. 예외 처리 및 안전장치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안전 공기 회복(/s)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>먼지·꽃가루·일반 연기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플레이어-적 거리(m)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 구간까지 필요한 호흡량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3. 선택 경로 적용 기준</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중복 상태·소리·모션 방지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BREATH_INHALE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거리 김 / 위험 낮음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수중 거리와 잔여 호흡량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유효 소리 감지 거리(m)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 시스템 응용 콘텐츠</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유해 공기·안전 공기·회복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참기와 조합 시 이동 소리 0m</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위장 상태에서 호흡 소리 제어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위험 구간 내 정상 이동 가능 시간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극 이상까지 남은 시간(s)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>눈 없는 인형 + 엄폐 / 통로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>회복 시간·다음 구간 필요 호흡량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안전 공기에서 자극도 80 이하</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시야 차단 + 호흡 소리 제어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>환경 게이지 기본 변화량(/s)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현재 행동 유지 가능 시간(s)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>벽 뒤 거리와 소리 감지 거리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유해 공기가 존재하는 연구실 등</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡량 확보 / 자극·오염 회복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>청각 × 1.5 / 최대 14m</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오염 사망까지 남은 시간(s)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>다음 위험 구간에 필요한 호흡 준비</x:t>
+  </x:si>
+  <x:si>
+    <x:t>숨을 참을 시점과 이동 타이밍</x:t>
+  </x:si>
+  <x:si>
+    <x:t>각 게이지의 개별 해제 조건 적용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 호흡 / 위험 공기 소량 흡입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>중복 호흡 판정과 모션 충돌 방지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5. 이동 소리 및 특수 조합</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오염 이상까지 남은 시간(s)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡 행동 유지 가능 시간(s)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반 연기 발생 → 자극도 누적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>청각 특화 / 시야 감지 없음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이상 상태 &gt; 과흡입·강제 호흡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 누적 +20/s</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 변화량(/s)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 기본 호흡 행동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지속 시간(s)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반 인형 구간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡량 0 : 익사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상한 초과 조작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해당 행동 유지 중</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오염도 50 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>날숨 강제 호흡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>위험 공기 흡입 배율</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불 인형 2단계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡량 변화(/s)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유예 시간(s)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적·위험 공기 없음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1. 구간 통과 검증</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불 인형 1단계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BREATH_HOLD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. 소리 감지 검증</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡 행동 연계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>구간 거리(m)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불 인형 초기 단계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시스템 변화·효과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작동 후 영구 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불 인형 최종 성장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불 인형 3단계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4. 이상 상태</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 소리 반경(m)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기침 소리 반경(m)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극 공기 구간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>입력·자동 전환 규칙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적 + 위험 공기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수중 호흡 규칙 적용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AI 감지 수치 고정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡량 생존 자원화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시야 거리(m)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>눈 없는 인형 구간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안전 지점 아이콘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>100 : 자극 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고정 수치 여부</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이동속도(m/s)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>최대 청각 거리(m)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2. 맵 적용 기준</x:t>
+  </x:si>
+  <x:si>
+    <x:t>반투명 환경 영역</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소리 발생 방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시야 없음 / 청각 민감도 × 1.5 / 최대 14m</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이상 상태·과흡입·호흡 중 머리가 잠기는 수중 진입</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참기 · 날숨은 기존 규칙 적용 / 들숨만-100/s</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적의 호흡 소리 감지 차단 / 위험 공기 흡입 차단</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장비 착용 중 / 적대 행동·충돌 등으로 노출 가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참기 + 웅크려 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>참기 강제 호흡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡량·환경 게이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡 / 소리 행동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플레이어 핵심 행동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안전 공기 + 엄폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>붉은 위험 구간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소리 반경(m)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>소리 감지 결과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>푸른 점선 동선</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발생 / 적용 조건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡량·재호흡 위치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>핵심 역할</x:t>
+  </x:si>
+  <x:si>
+    <x:t>평상 호흡</x:t>
+  </x:si>
+  <x:si>
+    <x:t>재준비 지점</x:t>
+  </x:si>
+  <x:si>
+    <x:t>검증 항목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>입력 항목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>예외 상황</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡 목적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>즉시 익사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극도 100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>웅크려 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극 환경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>환경 게이지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장치 작동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적용 규칙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플레이 선택</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3단계 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>눈 없는 인형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡량 확보</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배치 요소</x:t>
+  </x:si>
+  <x:si>
+    <x:t>무소음 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감지 판정</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감지 방식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>종료 후</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이벤트명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1초마다 1회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>청각 민감도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기침 주기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PPT 표현</x:t>
+  </x:si>
+  <x:si>
+    <x:t>환경 변화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우선 규칙</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유해 연기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현재 자극도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현재 오염도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적용 시스템</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오염도 회복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현재 호흡량</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지속 / 해제</x:t>
+  </x:si>
+  <x:si>
+    <x:t>산출 항목</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안전 구역</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이동 중 반복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>점프 착지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특수 환경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이동 속도</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극도 회복</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정상의 35%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착지 시 1회</x:t>
+  </x:si>
+  <x:si>
+    <x:t>발생 조건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡 처리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불 인형 성장</x:t>
+  </x:si>
+  <x:si>
+    <x:t>정상의 50%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은신 / 판별</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극 공기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>환경 조작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시야 + 소리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사다리 이동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>복합 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>방치 / 회피</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이동 행동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안전 아이콘</x:t>
+  </x:si>
+  <x:si>
+    <x:t>직선 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>안전 공기</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임계/사망</x:t>
+  </x:si>
+  <x:si>
+    <x:t>경로 유형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빠르게 통과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수중 구간</x:t>
+  </x:si>
+  <x:si>
+    <x:t>일반 인형</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡 행동</x:t>
+  </x:si>
+  <x:si>
+    <x:t>특수 조건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오염 환경</x:t>
+  </x:si>
+  <x:si>
+    <x:t>통과 불가능</x:t>
+  </x:si>
+  <x:si>
+    <x:t>우회 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>환기 장치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>오염 이상</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주요 판단</x:t>
+  </x:si>
+  <x:si>
+    <x:t>해제 조건</x:t>
+  </x:si>
+  <x:si>
+    <x:t>권장 표현</x:t>
   </x:si>
   <x:si>
     <x:t>구간 내 행동 가능 시간 = min(호흡 유지 가능 시간, 환경 위험 한계 시간) → 통과 가능 거리 = 이동속도 × 구간 내 행동 가능 시간</x:t>
   </x:si>
   <x:si>
-    <x:t>적의 호흡 소리 감지 차단 / 위험 공기 흡입 차단</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평상 호흡(호흡량 0)에서 날숨 새 입력 1초 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이상 상태·과흡입·호흡 중 머리가 잠기는 수중 진입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시야 없음 / 청각 민감도 × 1.5 / 최대 14m</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평상 호흡(호흡량 0)에서 참기 새 입력 1초 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장비 착용 중 / 적대 행동·충돌 등으로 노출 가능</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참기 · 날숨은 기존 규칙 적용 / 들숨만-100/s</x:t>
-  </x:si>
-  <x:si>
-    <x:t>욕조·침수 공간·공기 주머니</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3. 공기 환경 및 수중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플레이어-적 거리(m)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 구간까지 필요한 호흡량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시간 경과에 따라 다음 단계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡량 확보 / 상태 회복</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무소음 이동 가능 거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시야 방향 / 순찰 동선</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참기 + 웅크려 이동 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>신규 자극도 누적 차단</x:t>
-  </x:si>
-  <x:si>
-    <x:t>벽·가구 + 일반 인형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참기 시 이동 소리 0m</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡량 0 / 평상 호흡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>현재 행동 기준 통과 판정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7. 예외 처리 및 안전장치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2. 호흡 실패 이벤트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중복 상태·소리·모션 방지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>외형 판별 + 호흡 소리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3. 선택 경로 적용 기준</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거리 짧음 / 위험 높음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 시스템 응용 콘텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거리 김 / 위험 낮음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반 연기 발생 → 자극도 누적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참기와 조합 시 이동 소리 0m</x:t>
-  </x:si>
-  <x:si>
-    <x:t>청각 특화 / 시야 감지 없음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오염 이상까지 남은 시간(s)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위험 구간 내 정상 이동 가능 시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 호흡 / 위험 공기 소량 흡입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡량 확보 / 자극·오염 회복</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시야 차단 + 호흡 소리 제어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>현재 행동 유지 가능 시간(s)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오염 사망까지 남은 시간(s)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>중복 호흡 판정과 모션 충돌 방지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 위험 구간에 필요한 호흡 준비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>회복 시간·다음 구간 필요 호흡량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>눈 없는 인형 + 엄폐 / 통로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안전 공기에서 자극도 80 이하</x:t>
-  </x:si>
-  <x:si>
-    <x:t>청각 × 1.5 / 최대 14m</x:t>
-  </x:si>
-  <x:si>
-    <x:t>숨을 참을 시점과 이동 타이밍</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유해 공기가 존재하는 연구실 등</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5. 이동 소리 및 특수 조합</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극 이상까지 남은 시간(s)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡 행동 유지 가능 시간(s)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>벽 뒤 거리와 소리 감지 거리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>환경 게이지 기본 변화량(/s)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위장 상태에서 호흡 소리 제어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>각 게이지의 개별 해제 조건 적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이상 상태 &gt; 과흡입·강제 호흡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BREATH_NORMAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BREATH_EXHALE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>긴 이동 + 중간 안전 지점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통과 시간 / 현재 자극도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BREATH_INHALE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안전 공기 회복(/s)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유효 소리 감지 거리(m)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>6. 인형 감지 데이터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수중 거리와 잔여 호흡량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안전 공기에서 오염도 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>재준비 지점</x:t>
-  </x:si>
-  <x:si>
-    <x:t>눈 없는 인형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>장치 작동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적용 규칙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>청각 민감도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>즉시 익사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>검증 항목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극도 100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우선 규칙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>핵심 역할</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1초마다 1회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡 목적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>예외 상황</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플레이 선택</x:t>
-  </x:si>
-  <x:si>
-    <x:t>평상 호흡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감지 방식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배치 요소</x:t>
-  </x:si>
-  <x:si>
-    <x:t>환경 변화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PPT 표현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감지 판정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡량 확보</x:t>
-  </x:si>
-  <x:si>
-    <x:t>환경 게이지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극 환경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>입력 항목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기침 주기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>무소음 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이벤트명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>종료 후</x:t>
-  </x:si>
-  <x:si>
-    <x:t>웅크려 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3단계 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>발생 조건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이동 중 반복</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이동 속도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>환경 조작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지속 / 해제</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착지 시 1회</x:t>
-  </x:si>
-  <x:si>
-    <x:t>현재 호흡량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불 인형 성장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안전 구역</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오염도 회복</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정상의 50%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특수 환경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡 처리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극 공기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은신 / 판별</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시야 + 소리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>현재 자극도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사다리 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>점프 착지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>복합 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>먼지·꽃가루·일반 연기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유해 공기·안전 공기·회복</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참기 유지 · 날숨 여부를 조절하며 다음 공기 지점까지 호흡량 관리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직접 조작 불가 / 시스템상 평상 호흡 / 호흡량 -50/s → 0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유해 연기 발생 → 오염도 신규 누적
-/ 기존 자극도는 그대로 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡량</x:t>
-  </x:si>
-  <x:si>
-    <x:t>독가스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행동명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>-</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오염도</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t>값</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구분</x:t>
-  </x:si>
-  <x:si>
-    <x:t>콘텐츠</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>환경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>날숨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특징</x:t>
-  </x:si>
-  <x:si>
-    <x:t>미감지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과흡입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>결과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상태</x:t>
-  </x:si>
-  <x:si>
-    <x:t>없음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안전</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>분류</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시야각</x:t>
-  </x:si>
-  <x:si>
-    <x:t>걷기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달리기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수영</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구성</x:t>
-  </x:si>
-  <x:si>
-    <x:t>들숨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>연기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>꽃가루</x:t>
-  </x:si>
-  <x:si>
-    <x:t>처리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90˚</x:t>
-  </x:si>
-  <x:si>
-    <x:t>먼지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해당 행동 유지 중</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적·위험 공기 없음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>위험 공기 흡입 배율</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡량 변화(/s)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유예 시간(s)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지속 시간(s)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 누적 +20/s</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반 인형 구간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오염도 50 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불 인형 2단계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡량 0 : 익사</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상한 초과 조작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 기본 호흡 행동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>날숨 강제 호흡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불 인형 1단계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이동속도(m/s)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불 인형 초기 단계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2. 소리 감지 검증</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4. 이상 상태</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 변화량(/s)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BREATH_HOLD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 소리 반경(m)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시스템 변화·효과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작동 후 영구 유지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡 행동 연계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불 인형 3단계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기침 소리 반경(m)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1. 구간 통과 검증</x:t>
-  </x:si>
-  <x:si>
-    <x:t>구간 거리(m)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불 인형 최종 성장</x:t>
-  </x:si>
-  <x:si>
-    <x:t>계산·검증 시트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소리 발생 방식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시야 거리(m)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>최대 청각 거리(m)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>반투명 환경 영역</x:t>
-  </x:si>
-  <x:si>
-    <x:t>눈 없는 인형 구간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적 + 위험 공기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극 공기 구간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡량 생존 자원화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AI 감지 수치 고정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100 : 자극 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수중 호흡 규칙 적용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고정 수치 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안전 지점 아이콘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>입력·자동 전환 규칙</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2. 맵 적용 기준</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡량·재호흡 위치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>청각 중심 표시</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소리 감지 결과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>들숨·회복 후 재진입</x:t>
-  </x:si>
-  <x:si>
-    <x:t>발생 / 적용 조건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>붉은 위험 구간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주요 자원 판단</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플레이어 핵심 행동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참기 강제 호흡</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참기 유지 여부</x:t>
-  </x:si>
-  <x:si>
-    <x:t>소리 반경(m)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다음 구간 준비</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안전하게 돌아가기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>푸른 점선 동선</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡량·환경 게이지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>참기 + 웅크려 이동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안전 공기 + 엄폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡 / 소리 행동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>현재 오염도</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유해 연기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적용 시스템</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극도 회복</x:t>
-  </x:si>
-  <x:si>
-    <x:t>산출 항목</x:t>
-  </x:si>
-  <x:si>
-    <x:t>정상의 35%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이동 행동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수중 구간</x:t>
-  </x:si>
-  <x:si>
-    <x:t>직선 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안전 공기</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡 행동</x:t>
-  </x:si>
-  <x:si>
-    <x:t>통과 불가능</x:t>
-  </x:si>
-  <x:si>
-    <x:t>특수 조건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>방치 / 회피</x:t>
-  </x:si>
-  <x:si>
-    <x:t>해제 조건</x:t>
-  </x:si>
-  <x:si>
-    <x:t>권장 표현</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오염 환경</x:t>
-  </x:si>
-  <x:si>
-    <x:t>우회 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주요 판단</x:t>
-  </x:si>
-  <x:si>
-    <x:t>안전 아이콘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임계/사망</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오염 이상</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반 인형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빠르게 통과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>경로 유형</x:t>
-  </x:si>
-  <x:si>
-    <x:t>환기 장치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호흡량 100에서 들숨 입력을 계속 유지</x:t>
+    <x:t>호흡량 0에서 참기 입력을 1초 이상 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡량 0에서 날숨 입력을 1초 이상 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>현재 행동 기준 이동 가능 거리(m)</x:t>
   </x:si>
   <x:si>
     <x:t>과흡입·강제 호흡 중 이상 상태 발생</x:t>
   </x:si>
   <x:si>
-    <x:t>현재 행동 기준 이동 가능 거리(m)</x:t>
+    <x:t>일반 수중 호흡 판정 전에 즉시 익사 처리</x:t>
   </x:si>
   <x:si>
     <x:t>남은 호흡량 배출 / 평상 호흡 복귀</x:t>
   </x:si>
   <x:si>
+    <x:t>특정 인형 외형과 유사한 위장 장비 착용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50 : 오염 이상 / 100 : 사망</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극도 · 오염도 회복 -20/s 고정</x:t>
+  </x:si>
+  <x:si>
     <x:t>이동 가능 거리·안전 지점 도착 여부</x:t>
   </x:si>
   <x:si>
-    <x:t>특정 인형 외형과 유사한 위장 장비 착용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극도 · 오염도 회복 -20/s 고정</x:t>
-  </x:si>
-  <x:si>
-    <x:t>일반 수중 호흡 판정 전에 즉시 익사 처리</x:t>
-  </x:si>
-  <x:si>
     <x:t>3. 시스템에 필요한 밸런스 산출 공식</x:t>
   </x:si>
   <x:si>
-    <x:t>50 : 오염 이상 / 100 : 사망</x:t>
+    <x:t>기존 호흡 실패 상태 종료 → 이상 상태 전환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡 행동 적용 후 환경 게이지 변화량(/s)</x:t>
   </x:si>
   <x:si>
     <x:t>일반 연기 범위 확대 → 자극 위험 구간 확대</x:t>
   </x:si>
   <x:si>
-    <x:t>호흡 행동 적용 후 환경 게이지 변화량(/s)</x:t>
-  </x:si>
-  <x:si>
     <x:t>호흡 소리 0m + 이동 소리 0m로 무소음 이동</x:t>
   </x:si>
   <x:si>
-    <x:t>기존 호흡 실패 상태 종료 → 이상 상태 전환</x:t>
-  </x:si>
-  <x:si>
     <x:t>소리 발생 위치 조사 / 시야 직접 확인 시 추적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡량 100에서 들숨 입력을 1초 이상 유지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호흡량 0 / 조작 재개</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1429,50 +1432,18 @@
       <x:sz val="10"/>
       <x:color rgb="ff000000"/>
     </x:font>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="KoddiUD 온고딕 Regular"/>
-          <x:sz val="10"/>
-          <x:color rgb="ffffffff"/>
-          <x:b val="1"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="KoddiUD 온고딕 Regular"/>
-          <x:sz val="10"/>
-          <x:color rgb="ffffffff"/>
-          <x:b val="1"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
-        <x:font hs:extension="1">
-          <x:name val="KoddiUD 온고딕 Regular"/>
-          <x:sz val="10"/>
-          <x:color rgb="ff000000"/>
-          <x:b val="1"/>
-          <hs:size val="100"/>
-          <hs:ratio val="100"/>
-          <hs:spacing val="0"/>
-          <hs:offset val="0"/>
-        </x:font>
-      </mc:Choice>
-      <mc:Fallback>
-        <x:font>
-          <x:name val="KoddiUD 온고딕 Regular"/>
-          <x:sz val="10"/>
-          <x:color rgb="ff000000"/>
-          <x:b val="1"/>
-        </x:font>
-      </mc:Fallback>
-    </mc:AlternateContent>
+    <x:font>
+      <x:name val="KoddiUD 온고딕 Regular"/>
+      <x:sz val="10"/>
+      <x:color rgb="ffffffff"/>
+      <x:b val="1"/>
+    </x:font>
+    <x:font>
+      <x:name val="KoddiUD 온고딕 Regular"/>
+      <x:sz val="10"/>
+      <x:color rgb="ff000000"/>
+      <x:b val="1"/>
+    </x:font>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:font hs:extension="1">
@@ -1495,18 +1466,50 @@
         </x:font>
       </mc:Fallback>
     </mc:AlternateContent>
-    <x:font>
-      <x:name val="맑은 고딕"/>
-      <x:sz val="12"/>
-      <x:color rgb="ffffffff"/>
-      <x:b val="1"/>
-    </x:font>
-    <x:font>
-      <x:name val="KoddiUD 온고딕 Regular"/>
-      <x:sz val="15"/>
-      <x:color rgb="ffffffff"/>
-      <x:b val="1"/>
-    </x:font>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="맑은 고딕"/>
+          <x:sz val="12"/>
+          <x:color rgb="ffffffff"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="맑은 고딕"/>
+          <x:sz val="12"/>
+          <x:color rgb="ffffffff"/>
+          <x:b val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:font hs:extension="1">
+          <x:name val="KoddiUD 온고딕 Regular"/>
+          <x:sz val="15"/>
+          <x:color rgb="ffffffff"/>
+          <x:b val="1"/>
+          <hs:size val="100"/>
+          <hs:ratio val="100"/>
+          <hs:spacing val="0"/>
+          <hs:offset val="0"/>
+        </x:font>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:font>
+          <x:name val="KoddiUD 온고딕 Regular"/>
+          <x:sz val="15"/>
+          <x:color rgb="ffffffff"/>
+          <x:b val="1"/>
+        </x:font>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
         <x:font hs:extension="1">
@@ -3318,7 +3321,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:7" ht="30" customHeight="1">
       <x:c r="A1" s="63" t="s">
-        <x:v>193</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B1" s="63"/>
       <x:c r="C1" s="63"/>
@@ -3329,34 +3332,34 @@
     </x:row>
     <x:row r="2" spans="1:8" ht="30" customHeight="1">
       <x:c r="A2" s="46" t="s">
-        <x:v>178</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B2" s="46" t="s">
-        <x:v>143</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="46" t="s">
-        <x:v>184</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D2" s="46" t="s">
-        <x:v>237</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E2" s="46" t="s">
-        <x:v>183</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F2" s="47" t="s">
-        <x:v>93</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G2" s="47" t="s">
-        <x:v>225</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="H2" s="9"/>
     </x:row>
     <x:row r="3" spans="1:7" ht="30" customHeight="1">
       <x:c r="A3" s="48" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B3" s="48" t="s">
-        <x:v>99</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C3" s="49">
         <x:v>0</x:v>
@@ -3368,18 +3371,18 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="F3" s="50" t="s">
-        <x:v>53</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="G3" s="50" t="s">
-        <x:v>17</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7" ht="30" customHeight="1">
       <x:c r="A4" s="51" t="s">
-        <x:v>78</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B4" s="51" t="s">
-        <x:v>173</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C4" s="52">
         <x:v>50</x:v>
@@ -3391,18 +3394,18 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F4" s="53" t="s">
-        <x:v>106</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="G4" s="53" t="s">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7" ht="30" customHeight="1">
       <x:c r="A5" s="48" t="s">
-        <x:v>201</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B5" s="48" t="s">
-        <x:v>165</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C5" s="49">
         <x:v>-10</x:v>
@@ -3414,18 +3417,18 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="50" t="s">
-        <x:v>19</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="G5" s="50" t="s">
-        <x:v>1</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7" ht="30" customHeight="1">
       <x:c r="A6" s="51" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B6" s="51" t="s">
-        <x:v>153</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C6" s="52">
         <x:v>-66.700000000000003</x:v>
@@ -3440,7 +3443,7 @@
         <x:v>274</x:v>
       </x:c>
       <x:c r="G6" s="53" t="s">
-        <x:v>6</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8" ht="30" customHeight="1">
@@ -3455,7 +3458,7 @@
     </x:row>
     <x:row r="8" spans="1:7" ht="30" customHeight="1">
       <x:c r="A8" s="65" t="s">
-        <x:v>41</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B8" s="66"/>
       <x:c r="C8" s="66"/>
@@ -3466,33 +3469,33 @@
     </x:row>
     <x:row r="9" spans="1:7" ht="30" customHeight="1">
       <x:c r="A9" s="14" t="s">
-        <x:v>112</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B9" s="14" t="s">
-        <x:v>116</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C9" s="14" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
         <x:v>185</x:v>
       </x:c>
-      <x:c r="D9" s="14" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="E9" s="14" t="s">
-        <x:v>237</x:v>
-      </x:c>
       <x:c r="F9" s="14" t="s">
-        <x:v>113</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="G9" s="14" t="s">
-        <x:v>147</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7" ht="30" customHeight="1">
       <x:c r="A10" s="16" t="s">
-        <x:v>158</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="17" t="s">
-        <x:v>271</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="C10" s="18">
         <x:v>1</x:v>
@@ -3504,18 +3507,18 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="F10" s="16" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G10" s="16" t="s">
-        <x:v>192</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7" ht="30" customHeight="1">
       <x:c r="A11" s="2" t="s">
-        <x:v>235</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B11" s="8" t="s">
-        <x:v>23</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="C11" s="5">
         <x:v>1</x:v>
@@ -3527,18 +3530,18 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="F11" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="G11" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7" ht="30" customHeight="1">
       <x:c r="A12" s="16" t="s">
-        <x:v>194</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B12" s="17" t="s">
-        <x:v>20</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="C12" s="18">
         <x:v>1</x:v>
@@ -3550,16 +3553,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="F12" s="16" t="s">
-        <x:v>38</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="G12" s="16" t="s">
-        <x:v>16</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="30" customHeight="1"/>
     <x:row r="14" spans="1:7" ht="30" customHeight="1">
       <x:c r="A14" s="68" t="s">
-        <x:v>27</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B14" s="68"/>
       <x:c r="C14" s="68"/>
@@ -3570,36 +3573,36 @@
     </x:row>
     <x:row r="15" spans="1:7" ht="30" customHeight="1">
       <x:c r="A15" s="14" t="s">
-        <x:v>152</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B15" s="14" t="s">
-        <x:v>149</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C15" s="14" t="s">
-        <x:v>107</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D15" s="14" t="s">
-        <x:v>200</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E15" s="14" t="s">
-        <x:v>79</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F15" s="14" t="s">
-        <x:v>265</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="G15" s="14" t="s">
-        <x:v>87</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7" ht="30" customHeight="1">
       <x:c r="A16" s="16" t="s">
-        <x:v>254</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B16" s="16" t="s">
-        <x:v>164</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C16" s="16" t="s">
-        <x:v>169</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D16" s="18">
         <x:v>-20</x:v>
@@ -3608,21 +3611,21 @@
         <x:v>-20</x:v>
       </x:c>
       <x:c r="F16" s="16" t="s">
-        <x:v>144</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G16" s="16" t="s">
-        <x:v>248</x:v>
+        <x:v>235</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7" ht="30" customHeight="1">
       <x:c r="A17" s="2" t="s">
-        <x:v>254</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="B17" s="2" t="s">
-        <x:v>164</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C17" s="2" t="s">
-        <x:v>145</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D17" s="5">
         <x:v>-20</x:v>
@@ -3631,21 +3634,21 @@
         <x:v>-20</x:v>
       </x:c>
       <x:c r="F17" s="2" t="s">
-        <x:v>144</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7" ht="30" customHeight="1">
       <x:c r="A18" s="16" t="s">
-        <x:v>180</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B18" s="16" t="s">
-        <x:v>108</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C18" s="16" t="s">
-        <x:v>169</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D18" s="18">
         <x:v>20</x:v>
@@ -3654,21 +3657,21 @@
         <x:v>-20</x:v>
       </x:c>
       <x:c r="F18" s="16" t="s">
-        <x:v>221</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G18" s="16" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7" ht="30" customHeight="1">
       <x:c r="A19" s="2" t="s">
-        <x:v>175</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>108</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C19" s="2" t="s">
-        <x:v>169</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D19" s="5">
         <x:v>20</x:v>
@@ -3677,21 +3680,21 @@
         <x:v>-20</x:v>
       </x:c>
       <x:c r="F19" s="2" t="s">
-        <x:v>221</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G19" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7" ht="30" customHeight="1">
       <x:c r="A20" s="16" t="s">
-        <x:v>174</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B20" s="19" t="s">
-        <x:v>108</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="C20" s="16" t="s">
-        <x:v>169</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D20" s="18">
         <x:v>20</x:v>
@@ -3700,21 +3703,21 @@
         <x:v>-20</x:v>
       </x:c>
       <x:c r="F20" s="16" t="s">
-        <x:v>221</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="G20" s="19" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7" ht="30" customHeight="1">
       <x:c r="A21" s="2" t="s">
-        <x:v>246</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B21" s="2" t="s">
-        <x:v>261</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C21" s="2" t="s">
-        <x:v>145</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D21" s="5">
         <x:v>25</x:v>
@@ -3723,21 +3726,21 @@
         <x:v>-20</x:v>
       </x:c>
       <x:c r="F21" s="2" t="s">
-        <x:v>280</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="G21" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7" ht="30" customHeight="1">
       <x:c r="A22" s="16" t="s">
-        <x:v>142</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="19" t="s">
-        <x:v>261</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="C22" s="16" t="s">
-        <x:v>145</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D22" s="18">
         <x:v>25</x:v>
@@ -3746,39 +3749,39 @@
         <x:v>-20</x:v>
       </x:c>
       <x:c r="F22" s="16" t="s">
-        <x:v>280</x:v>
+        <x:v>276</x:v>
       </x:c>
       <x:c r="G22" s="16" t="s">
-        <x:v>8</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7" ht="30" customHeight="1">
       <x:c r="A23" s="2" t="s">
-        <x:v>159</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B23" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C23" s="2" t="s">
-        <x:v>141</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D23" s="5" t="s">
-        <x:v>144</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E23" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F23" s="2" t="s">
-        <x:v>191</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="G23" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="30" customHeight="1"/>
     <x:row r="25" spans="1:7" ht="30" customHeight="1">
       <x:c r="A25" s="68" t="s">
-        <x:v>199</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B25" s="68"/>
       <x:c r="C25" s="68"/>
@@ -3789,100 +3792,100 @@
     </x:row>
     <x:row r="26" spans="1:7" ht="30" customHeight="1">
       <x:c r="A26" s="14" t="s">
-        <x:v>161</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B26" s="14" t="s">
-        <x:v>116</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C26" s="14" t="s">
-        <x:v>259</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="D26" s="14" t="s">
-        <x:v>118</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="E26" s="14" t="s">
-        <x:v>110</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="F26" s="14" t="s">
-        <x:v>207</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="G26" s="14" t="s">
-        <x:v>128</x:v>
+        <x:v>239</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7" ht="30" customHeight="1">
       <x:c r="A27" s="16" t="s">
-        <x:v>94</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="B27" s="16" t="s">
-        <x:v>91</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C27" s="16" t="s">
-        <x:v>62</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D27" s="16" t="s">
-        <x:v>126</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="E27" s="16" t="s">
-        <x:v>95</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F27" s="18">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G27" s="16" t="s">
-        <x:v>139</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7" ht="30" customHeight="1">
       <x:c r="A28" s="2" t="s">
-        <x:v>266</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="B28" s="2" t="s">
-        <x:v>189</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C28" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D28" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="E28" s="2" t="s">
-        <x:v>95</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F28" s="5">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G28" s="2" t="s">
-        <x:v>139</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7" ht="30" customHeight="1">
       <x:c r="A29" s="16" t="s">
-        <x:v>135</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B29" s="16" t="s">
-        <x:v>3</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C29" s="16" t="s">
-        <x:v>72</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D29" s="16" t="s">
-        <x:v>250</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="E29" s="16" t="s">
-        <x:v>95</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="F29" s="18">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G29" s="16" t="s">
-        <x:v>139</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="30" customHeight="1"/>
     <x:row r="31" spans="1:7" ht="30" customHeight="1">
       <x:c r="A31" s="68" t="s">
-        <x:v>66</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B31" s="68"/>
       <x:c r="C31" s="68"/>
@@ -3893,141 +3896,141 @@
     </x:row>
     <x:row r="32" spans="1:7" ht="30" customHeight="1">
       <x:c r="A32" s="15" t="s">
-        <x:v>251</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B32" s="10" t="s">
-        <x:v>237</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C32" s="70" t="s">
-        <x:v>257</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="D32" s="71"/>
       <x:c r="E32" s="72" t="s">
-        <x:v>212</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="F32" s="73"/>
       <x:c r="G32" s="11" t="s">
-        <x:v>205</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7" ht="30" customHeight="1">
       <x:c r="A33" s="16" t="s">
-        <x:v>114</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B33" s="20">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C33" s="74" t="s">
-        <x:v>49</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D33" s="75"/>
       <x:c r="E33" s="76" t="s">
-        <x:v>117</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F33" s="77"/>
       <x:c r="G33" s="21" t="s">
-        <x:v>37</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7" ht="30" customHeight="1">
       <x:c r="A34" s="2" t="s">
-        <x:v>168</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B34" s="7">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C34" s="78" t="s">
-        <x:v>144</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D34" s="79"/>
       <x:c r="E34" s="80" t="s">
-        <x:v>117</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F34" s="81"/>
       <x:c r="G34" s="6" t="s">
-        <x:v>144</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7" ht="30" customHeight="1">
       <x:c r="A35" s="16" t="s">
-        <x:v>133</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="B35" s="20">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C35" s="74" t="s">
-        <x:v>144</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D35" s="75"/>
       <x:c r="E35" s="82" t="s">
-        <x:v>117</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F35" s="77"/>
       <x:c r="G35" s="21" t="s">
-        <x:v>144</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7" ht="30" customHeight="1">
       <x:c r="A36" s="2" t="s">
-        <x:v>171</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B36" s="7">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C36" s="78" t="s">
-        <x:v>144</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D36" s="79"/>
       <x:c r="E36" s="80" t="s">
-        <x:v>117</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F36" s="81"/>
       <x:c r="G36" s="6" t="s">
-        <x:v>222</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7" ht="30" customHeight="1">
       <x:c r="A37" s="16" t="s">
-        <x:v>170</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B37" s="20">
         <x:v>7</x:v>
       </x:c>
       <x:c r="C37" s="74" t="s">
-        <x:v>144</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D37" s="75"/>
       <x:c r="E37" s="76" t="s">
-        <x:v>117</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="F37" s="77"/>
       <x:c r="G37" s="21" t="s">
-        <x:v>144</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7" ht="30" customHeight="1">
       <x:c r="A38" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="B38" s="7">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="78" t="s">
-        <x:v>144</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D38" s="79"/>
       <x:c r="E38" s="83" t="s">
-        <x:v>121</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="F38" s="84"/>
       <x:c r="G38" s="6" t="s">
-        <x:v>144</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="30" customHeight="1"/>
     <x:row r="40" spans="1:7" ht="30" customHeight="1">
       <x:c r="A40" s="85" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B40" s="68"/>
       <x:c r="C40" s="68"/>
@@ -4038,36 +4041,36 @@
     </x:row>
     <x:row r="41" spans="1:7" ht="30" customHeight="1">
       <x:c r="A41" s="10" t="s">
-        <x:v>105</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="B41" s="14" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="C41" s="14" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D41" s="14" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="E41" s="14" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="F41" s="14" t="s">
         <x:v>213</x:v>
       </x:c>
-      <x:c r="C41" s="14" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="D41" s="14" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E41" s="14" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="F41" s="14" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="G41" s="14" t="s">
-        <x:v>229</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7" ht="30" customHeight="1">
       <x:c r="A42" s="16" t="s">
-        <x:v>267</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B42" s="18">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C42" s="18" t="s">
-        <x:v>179</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D42" s="18">
         <x:v>1</x:v>
@@ -4076,21 +4079,21 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F42" s="16" t="s">
-        <x:v>131</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="G42" s="16" t="s">
-        <x:v>285</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7" ht="30" customHeight="1">
       <x:c r="A43" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B43" s="5">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C43" s="5" t="s">
-        <x:v>162</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D43" s="5">
         <x:v>1.5</x:v>
@@ -4099,16 +4102,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F43" s="2" t="s">
-        <x:v>154</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G43" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="30" customHeight="1"/>
     <x:row r="45" spans="1:7" ht="30" customHeight="1">
       <x:c r="A45" s="68" t="s">
-        <x:v>40</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B45" s="68"/>
       <x:c r="C45" s="68"/>
@@ -4119,36 +4122,36 @@
     </x:row>
     <x:row r="46" spans="1:7" ht="30" customHeight="1">
       <x:c r="A46" s="86" t="s">
-        <x:v>97</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B46" s="87"/>
       <x:c r="C46" s="86" t="s">
-        <x:v>176</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D46" s="87"/>
       <x:c r="E46" s="86" t="s">
-        <x:v>92</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="F46" s="87"/>
       <x:c r="G46" s="14" t="s">
-        <x:v>177</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7" ht="30" customHeight="1">
       <x:c r="A47" s="88" t="s">
-        <x:v>21</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="B47" s="89"/>
       <x:c r="C47" s="90" t="s">
-        <x:v>89</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="D47" s="89"/>
       <x:c r="E47" s="90" t="s">
-        <x:v>278</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="F47" s="88"/>
       <x:c r="G47" s="19" t="s">
-        <x:v>58</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7" ht="30" customHeight="1">
@@ -4157,15 +4160,15 @@
       </x:c>
       <x:c r="B48" s="92"/>
       <x:c r="C48" s="93" t="s">
-        <x:v>284</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D48" s="92"/>
       <x:c r="E48" s="93" t="s">
-        <x:v>73</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F48" s="91"/>
       <x:c r="G48" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4226,7 +4229,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A1" s="94" t="s">
-        <x:v>46</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B1" s="94"/>
       <x:c r="C1" s="94"/>
@@ -4237,169 +4240,169 @@
     </x:row>
     <x:row r="2" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A2" s="41" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B2" s="41" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C2" s="41" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="D2" s="41" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="E2" s="41" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="F2" s="41" t="s">
         <x:v>150</x:v>
       </x:c>
-      <x:c r="B2" s="41" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="C2" s="41" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="D2" s="41" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="E2" s="41" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="F2" s="41" t="s">
-        <x:v>203</x:v>
-      </x:c>
       <x:c r="G2" s="41" t="s">
-        <x:v>120</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A3" s="42" t="s">
-        <x:v>85</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="B3" s="42" t="s">
-        <x:v>151</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="43" t="s">
-        <x:v>2</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D3" s="42" t="s">
-        <x:v>22</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="E3" s="42" t="s">
-        <x:v>242</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="F3" s="42" t="s">
         <x:v>283</x:v>
       </x:c>
       <x:c r="G3" s="42" t="s">
-        <x:v>181</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A4" s="44" t="s">
-        <x:v>163</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="44" t="s">
-        <x:v>130</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="C4" s="45" t="s">
-        <x:v>43</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D4" s="44" t="s">
-        <x:v>276</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="E4" s="44" t="s">
-        <x:v>71</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="F4" s="44" t="s">
-        <x:v>14</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G4" s="44" t="s">
-        <x:v>24</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A5" s="42" t="s">
-        <x:v>270</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B5" s="42" t="s">
-        <x:v>119</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="C5" s="43" t="s">
-        <x:v>137</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D5" s="42" t="s">
-        <x:v>65</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E5" s="42" t="s">
-        <x:v>86</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="F5" s="42" t="s">
-        <x:v>7</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G5" s="42" t="s">
-        <x:v>204</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A6" s="44" t="s">
-        <x:v>195</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B6" s="44" t="s">
-        <x:v>102</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C6" s="45" t="s">
-        <x:v>129</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="D6" s="44" t="s">
-        <x:v>197</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E6" s="44" t="s">
-        <x:v>258</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="F6" s="44" t="s">
-        <x:v>48</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G6" s="44" t="s">
-        <x:v>30</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A7" s="42" t="s">
-        <x:v>190</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B7" s="42" t="s">
-        <x:v>102</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C7" s="43" t="s">
-        <x:v>129</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="D7" s="42" t="s">
-        <x:v>123</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E7" s="42" t="s">
-        <x:v>258</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="F7" s="42" t="s">
-        <x:v>281</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="G7" s="42" t="s">
-        <x:v>30</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A8" s="44" t="s">
-        <x:v>206</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B8" s="44" t="s">
-        <x:v>102</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C8" s="45" t="s">
-        <x:v>137</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D8" s="44" t="s">
-        <x:v>210</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E8" s="44" t="s">
-        <x:v>258</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="F8" s="44" t="s">
-        <x:v>140</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G8" s="44" t="s">
-        <x:v>115</x:v>
+        <x:v>207</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30.75" customHeight="1"/>
     <x:row r="10" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A10" s="95" t="s">
-        <x:v>226</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="B10" s="95"/>
       <x:c r="C10" s="95"/>
@@ -4410,146 +4413,146 @@
     </x:row>
     <x:row r="11" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A11" s="12" t="s">
-        <x:v>157</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B11" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C11" s="12" t="s">
-        <x:v>96</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D11" s="12" t="s">
-        <x:v>263</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="E11" s="12" t="s">
-        <x:v>260</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="F11" s="12" t="s">
-        <x:v>223</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="G11" s="12" t="s">
-        <x:v>90</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A12" s="16" t="s">
-        <x:v>124</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="B12" s="16" t="s">
-        <x:v>182</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C12" s="16" t="s">
-        <x:v>31</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D12" s="16" t="s">
-        <x:v>59</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E12" s="16" t="s">
-        <x:v>224</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="F12" s="16" t="s">
         <x:v>277</x:v>
       </x:c>
       <x:c r="G12" s="16" t="s">
-        <x:v>29</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A13" s="2" t="s">
-        <x:v>188</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B13" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C13" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E13" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F13" s="2" t="s">
-        <x:v>220</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="G13" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A14" s="16" t="s">
-        <x:v>218</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B14" s="16" t="s">
-        <x:v>136</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C14" s="16" t="s">
-        <x:v>35</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D14" s="16" t="s">
-        <x:v>236</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E14" s="16" t="s">
-        <x:v>215</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="F14" s="16" t="s">
-        <x:v>187</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G14" s="16" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A15" s="2" t="s">
-        <x:v>216</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="B15" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C15" s="2" t="s">
-        <x:v>111</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E15" s="2" t="s">
-        <x:v>228</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F15" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G15" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A16" s="16" t="s">
-        <x:v>252</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="B16" s="16" t="s">
-        <x:v>26</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C16" s="16" t="s">
-        <x:v>219</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="D16" s="16" t="s">
-        <x:v>138</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E16" s="16" t="s">
-        <x:v>4</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F16" s="22" t="s">
-        <x:v>25</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G16" s="16" t="s">
-        <x:v>82</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="30.75" customHeight="1"/>
     <x:row r="18" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A18" s="96" t="s">
-        <x:v>44</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B18" s="96"/>
       <x:c r="C18" s="96"/>
@@ -4560,48 +4563,48 @@
     </x:row>
     <x:row r="19" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A19" s="13" t="s">
-        <x:v>269</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="B19" s="13" t="s">
-        <x:v>172</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C19" s="13" t="s">
-        <x:v>155</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D19" s="13" t="s">
-        <x:v>233</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E19" s="13" t="s">
-        <x:v>98</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="F19" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="G19" s="13" t="s">
-        <x:v>103</x:v>
+        <x:v>219</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A20" s="19" t="s">
-        <x:v>253</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B20" s="19" t="s">
-        <x:v>217</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C20" s="19" t="s">
-        <x:v>45</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D20" s="19" t="s">
-        <x:v>241</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="E20" s="19" t="s">
-        <x:v>268</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="F20" s="19" t="s">
-        <x:v>52</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G20" s="19" t="s">
-        <x:v>232</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7" ht="30.75" customHeight="1">
@@ -4609,45 +4612,45 @@
         <x:v>262</x:v>
       </x:c>
       <x:c r="B21" s="3" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C21" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D21" s="3" t="s">
-        <x:v>227</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E21" s="3" t="s">
-        <x:v>239</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F21" s="3" t="s">
-        <x:v>275</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="G21" s="3" t="s">
-        <x:v>240</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7" ht="30.75" customHeight="1">
       <x:c r="A22" s="19" t="s">
-        <x:v>84</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B22" s="19" t="s">
-        <x:v>243</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C22" s="19" t="s">
-        <x:v>54</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D22" s="19" t="s">
-        <x:v>238</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E22" s="19" t="s">
-        <x:v>230</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F22" s="19" t="s">
-        <x:v>60</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G22" s="19" t="s">
-        <x:v>264</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="30.75" customHeight="1"/>
@@ -4697,7 +4700,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:9" ht="30.39999999999999857891" customHeight="1">
       <x:c r="A1" s="97" t="s">
-        <x:v>211</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B1" s="98"/>
       <x:c r="C1" s="98"/>
@@ -4710,7 +4713,7 @@
     </x:row>
     <x:row r="2" spans="1:9" ht="30.39999999999999857891" customHeight="1">
       <x:c r="A2" s="99" t="s">
-        <x:v>0</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B2" s="99"/>
       <x:c r="C2" s="99"/>
@@ -4724,13 +4727,13 @@
     <x:row r="3" ht="15.75" customHeight="1"/>
     <x:row r="4" spans="1:9" ht="30.75" customHeight="1">
       <x:c r="A4" s="100" t="s">
-        <x:v>208</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B4" s="100"/>
       <x:c r="C4" s="100"/>
       <x:c r="D4" s="100"/>
       <x:c r="F4" s="101" t="s">
-        <x:v>198</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="G4" s="101"/>
       <x:c r="H4" s="101"/>
@@ -4738,52 +4741,52 @@
     </x:row>
     <x:row r="5" spans="1:9" ht="30.75" customHeight="1">
       <x:c r="A5" s="24" t="s">
-        <x:v>109</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B5" s="25" t="s">
-        <x:v>148</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C5" s="24" t="s">
-        <x:v>249</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="D5" s="25" t="s">
-        <x:v>160</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F5" s="26" t="s">
-        <x:v>109</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G5" s="27" t="s">
-        <x:v>148</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H5" s="26" t="s">
-        <x:v>249</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="I5" s="27" t="s">
-        <x:v>160</x:v>
+        <x:v>40</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9" ht="30.75" customHeight="1">
       <x:c r="A6" s="28" t="s">
-        <x:v>122</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B6" s="29">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C6" s="28" t="s">
-        <x:v>107</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D6" s="29" t="str">
         <x:f>VLOOKUP(B8,'01_시스템데이터'!$A$18:$D$22,3,FALSE)</x:f>
         <x:v>오염도</x:v>
       </x:c>
       <x:c r="F6" s="30" t="s">
-        <x:v>244</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="G6" s="31" t="s">
-        <x:v>165</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H6" s="30" t="s">
-        <x:v>202</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="I6" s="31">
         <x:f>IFERROR(VLOOKUP(G6,'01_시스템데이터'!$B$3:$D$6,3,0),IFERROR(VLOOKUP(G6,'01_시스템데이터'!$A$10:$E$12,5,0),VLOOKUP(G6,'01_시스템데이터'!$A$33:$B$38,2,0)))</x:f>
@@ -4792,26 +4795,26 @@
     </x:row>
     <x:row r="7" spans="1:9" ht="30.75" customHeight="1">
       <x:c r="A7" s="32" t="s">
-        <x:v>255</x:v>
+        <x:v>258</x:v>
       </x:c>
       <x:c r="B7" s="33" t="s">
-        <x:v>99</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C7" s="34" t="s">
-        <x:v>183</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D7" s="33">
         <x:f>VLOOKUP(B7,'01_시스템데이터'!$B$3:$E$6,4,FALSE)</x:f>
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="F7" s="34" t="s">
-        <x:v>105</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G7" s="35" t="s">
-        <x:v>85</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="H7" s="34" t="s">
-        <x:v>88</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="I7" s="35">
         <x:f>VLOOKUP(G7,'01_시스템데이터'!$A$42:$E$43,4,FALSE)</x:f>
@@ -4820,26 +4823,26 @@
     </x:row>
     <x:row r="8" spans="1:9" ht="30.75" customHeight="1">
       <x:c r="A8" s="28" t="s">
-        <x:v>152</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B8" s="29" t="s">
-        <x:v>246</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C8" s="30" t="s">
-        <x:v>70</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D8" s="29">
         <x:f>VLOOKUP(B8,'01_시스템데이터'!$A$18:$D$22,4,FALSE)</x:f>
         <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="54" t="s">
-        <x:v>28</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="G8" s="55">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H8" s="30" t="s">
-        <x:v>214</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="I8" s="31">
         <x:f>VLOOKUP(G7,'01_시스템데이터'!$A$42:$E$43,5,FALSE)</x:f>
@@ -4848,13 +4851,13 @@
     </x:row>
     <x:row r="9" spans="1:9" ht="30.75" customHeight="1">
       <x:c r="A9" s="32" t="s">
-        <x:v>132</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B9" s="33">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="32" t="s">
-        <x:v>282</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="D9" s="33">
         <x:f>IF(OR(D7="",D8=""),"",D7*D8)</x:f>
@@ -4863,7 +4866,7 @@
       <x:c r="F9" s="56"/>
       <x:c r="G9" s="56"/>
       <x:c r="H9" s="60" t="s">
-        <x:v>80</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="I9" s="36">
         <x:f>IF(OR(I6="",I7="",I8=""),"",MIN(I6*I7,I8))</x:f>
@@ -4872,13 +4875,13 @@
     </x:row>
     <x:row r="10" spans="1:9" ht="30.75" customHeight="1">
       <x:c r="A10" s="28" t="s">
-        <x:v>245</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="B10" s="29">
         <x:v>10</x:v>
       </x:c>
       <x:c r="C10" s="28" t="s">
-        <x:v>68</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D10" s="29" t="str">
         <x:f>IF(B7="들숨",MAX(0,(100-B6)/VLOOKUP(B7,'01_시스템데이터'!$B$3:$C$6,2,FALSE))+VLOOKUP("과흡입",'01_시스템데이터'!$A$10:$C$12,3,FALSE),IF(VLOOKUP(B7,'01_시스템데이터'!$B$3:$C$6,2,FALSE)&lt;0,B6/ABS(VLOOKUP(B7,'01_시스템데이터'!$B$3:$C$6,2,FALSE)),""))</x:f>
@@ -4887,7 +4890,7 @@
       <x:c r="F10" s="56"/>
       <x:c r="G10" s="56"/>
       <x:c r="H10" s="61" t="s">
-        <x:v>104</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="I10" s="62" t="str">
         <x:f>IF(G6="","행동 선택 필요",IF(G7="","적 유형 선택 필요",IF(G8="","거리 입력 필요",IF(I9="","계산 조건 확인",IF(G8&lt;=I9,"감지","미감지")))))</x:f>
@@ -4896,13 +4899,13 @@
     </x:row>
     <x:row r="11" spans="1:4" ht="30.75" customHeight="1">
       <x:c r="A11" s="32" t="s">
-        <x:v>196</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="B11" s="33">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C11" s="32" t="s">
-        <x:v>67</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D11" s="33" t="str">
         <x:f>IF(AND(D6="자극도",D9&gt;0),MAX(0,(100-B9)/D9),"")</x:f>
@@ -4911,20 +4914,20 @@
     </x:row>
     <x:row r="12" spans="1:9" ht="30.75" customHeight="1">
       <x:c r="A12" s="37" t="s">
-        <x:v>209</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B12" s="38">
         <x:v>5</x:v>
       </x:c>
       <x:c r="C12" s="28" t="s">
-        <x:v>51</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D12" s="29">
         <x:f>IF(AND(D6="오염도",D9&gt;0),MAX(0,(50-B10)/D9),"")</x:f>
         <x:v>3.2000000000000002</x:v>
       </x:c>
       <x:c r="F12" s="102" t="s">
-        <x:v>10</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G12" s="102"/>
       <x:c r="H12" s="102"/>
@@ -4932,7 +4935,7 @@
     </x:row>
     <x:row r="13" spans="3:4" ht="30.75" customHeight="1">
       <x:c r="C13" s="32" t="s">
-        <x:v>57</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D13" s="33">
         <x:f>IF(AND(D6="오염도",D9&gt;0),MAX(0,(100-B10)/D9),"")</x:f>
@@ -4941,11 +4944,11 @@
     </x:row>
     <x:row r="14" spans="1:4" ht="30.75" customHeight="1">
       <x:c r="A14" s="103" t="s">
-        <x:v>13</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B14" s="103"/>
       <x:c r="C14" s="28" t="s">
-        <x:v>56</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D14" s="29">
         <x:f>IF(D6="자극도",IF(D10="",D11,IF(D11="",D10,MIN(D10,D11))),IF(D6="오염도",IF(D10="",D12,IF(D12="",D10,MIN(D10,D12))),""))</x:f>
@@ -4954,7 +4957,7 @@
     </x:row>
     <x:row r="15" spans="3:4" ht="30.75" customHeight="1">
       <x:c r="C15" s="57" t="s">
-        <x:v>273</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="D15" s="39">
         <x:f>IF(OR(B11="",D14=""),"",B11*D14)</x:f>
@@ -4963,7 +4966,7 @@
     </x:row>
     <x:row r="16" spans="3:4" ht="30.75" customHeight="1">
       <x:c r="C16" s="58" t="s">
-        <x:v>39</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D16" s="59" t="str">
         <x:f>IF(B11="","이동속도 입력 필요",IF(B12="","구간 거리 입력 필요",IF(D14="","계산 조건 확인",IF(D15&gt;=B12,"통과 가능","통과 불가능"))))</x:f>
@@ -4981,7 +4984,7 @@
     </x:row>
     <x:row r="19" spans="1:9" ht="30.75" customHeight="1">
       <x:c r="A19" s="104" t="s">
-        <x:v>18</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="B19" s="104"/>
       <x:c r="C19" s="104"/>
